--- a/output/pdf_financials_xlsx/GSKR.xlsx
+++ b/output/pdf_financials_xlsx/GSKR.xlsx
@@ -804,10 +804,10 @@
         <v>0.012</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>0.448432</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>0.607642</v>
       </c>
     </row>
     <row r="10">
@@ -4852,19 +4852,19 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.703462</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.343591</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.618663</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.957091</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.655652</v>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
@@ -4872,19 +4872,19 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.442381</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.533113</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.81943</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>9.468862</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.897866</v>
       </c>
     </row>
     <row r="93">
@@ -8198,7 +8198,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -9054,7 +9058,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -9650,7 +9658,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -10284,7 +10296,11 @@
           <t>Reserves (Note 6) 703,462</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -16242,7 +16258,11 @@
           <t>Royalty expense (Note 6)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GSKR.xlsx
+++ b/output/pdf_financials_xlsx/GSKR.xlsx
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005306</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.027319</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.026586</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000738</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001534</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.468301</v>
       </c>
     </row>
     <row r="13">
@@ -1671,13 +1671,13 @@
         <v>-2.122888</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.770731</v>
+        <v>-2.776037</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.884689</v>
+        <v>-2.912008</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.128944</v>
+        <v>-2.15553</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1691,13 +1691,13 @@
         <v>-1.665625</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.827526</v>
+        <v>-1.826788</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-10.864315</v>
+        <v>-10.862781</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-28.235906</v>
+        <v>-27.767605</v>
       </c>
     </row>
     <row r="28">
@@ -1765,13 +1765,13 @@
         <v>-2.122888</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.770731</v>
+        <v>-2.776037</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.884689</v>
+        <v>-2.912008</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.128944</v>
+        <v>-2.15553</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1785,13 +1785,13 @@
         <v>-1.665625</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.827526</v>
+        <v>-1.826788</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-10.864315</v>
+        <v>-10.862781</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-28.235906</v>
+        <v>-27.767605</v>
       </c>
     </row>
     <row r="30">
@@ -1994,19 +1994,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.432767</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.91399</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.61847</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.09517</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.046462</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.284202</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.253348</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.128236</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>9.568671</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>84.381333</v>
       </c>
     </row>
     <row r="35">
@@ -2088,19 +2088,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.432767</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.91399</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.61847</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.09517</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.046462</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -2108,19 +2108,19 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.284202</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.253348</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.128236</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>9.568671</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>84.381333</v>
       </c>
     </row>
     <row r="37">
@@ -2652,19 +2652,19 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.437172</v>
+        <v>0.004405</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.91399</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.668229</v>
+        <v>0.049759</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.117673</v>
+        <v>0.022503</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.084561</v>
+        <v>0.038099</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -2672,19 +2672,19 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.326895</v>
+        <v>0.042693</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.258765</v>
+        <v>0.005417</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.43028</v>
+        <v>0.302044</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>10.796293</v>
+        <v>1.227622</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>85.05169100000001</v>
+        <v>0.670358</v>
       </c>
     </row>
     <row r="49">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">

--- a/output/pdf_financials_xlsx/GSKR.xlsx
+++ b/output/pdf_financials_xlsx/GSKR.xlsx
@@ -11590,7 +11590,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
